--- a/ky/downloads/data-excel/2.1.1.1.xlsx
+++ b/ky/downloads/data-excel/2.1.1.1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Национальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Национальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F77360-68D3-4A54-8B1D-C9AD22AAD0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10425"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="3" r:id="rId1"/>
@@ -66,15 +67,6 @@
     <t>Items</t>
   </si>
   <si>
-    <t>2.1.1.1e Среднедушевое потребление основных продуктов питания по отношению к среднефизиологическим нормам потребления</t>
-  </si>
-  <si>
-    <t>2.1.1.1e Average per capita consumption of basic food products in relation to the average physiological norms of consumption, in</t>
-  </si>
-  <si>
-    <t>2.1.1.1е Ортофизиологиалык керектөө ченемдерге карата негизги тамак-аш азыктарын орточо керектөөсү, пайыз менен</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Пшеница и продукты ее переработки, в муке</t>
   </si>
   <si>
@@ -136,12 +128,21 @@
   </si>
   <si>
     <t>Балык жана балык азыктары</t>
+  </si>
+  <si>
+    <t>2.1.1.1 Ортофизиологиалык керектөө ченемдерге карата негизги тамак-аш азыктарын орточо керектөөсү, пайыз менен</t>
+  </si>
+  <si>
+    <t>2.1.1.1 Среднедушевое потребление основных продуктов питания по отношению к среднефизиологическим нормам потребления</t>
+  </si>
+  <si>
+    <t>2.1.1.1 Average per capita consumption of basic food products in relation to the average physiological norms of consumption, in</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -229,7 +230,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -268,9 +269,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -308,9 +309,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -345,7 +346,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -380,7 +381,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -553,23 +554,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="38.42578125" style="7" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -581,7 +582,7 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -601,7 +602,7 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:17" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -619,8 +620,9 @@
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
       <c r="Q3" s="9"/>
-    </row>
-    <row r="4" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="R3" s="9"/>
+    </row>
+    <row r="4" spans="1:18" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
@@ -672,16 +674,19 @@
       <c r="Q4" s="5">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R4" s="5">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D5" s="10">
         <v>63.132137030995118</v>
@@ -723,18 +728,21 @@
         <v>76.508972267536706</v>
       </c>
       <c r="Q5" s="10">
-        <v>74.605426356589135</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>75.7</v>
+      </c>
+      <c r="R5" s="10">
+        <v>83.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D6" s="10">
         <v>106.2</v>
@@ -776,18 +784,21 @@
         <v>110.15000000000002</v>
       </c>
       <c r="Q6" s="10">
-        <v>118.8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>119.3</v>
+      </c>
+      <c r="R6" s="10">
+        <v>115.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D7" s="10">
         <v>43.506849315068493</v>
@@ -829,18 +840,21 @@
         <v>66.630136986301366</v>
       </c>
       <c r="Q7" s="10">
-        <v>71.61643835616438</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>72.599999999999994</v>
+      </c>
+      <c r="R7" s="10">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D8" s="10">
         <v>83.203125</v>
@@ -882,18 +896,21 @@
         <v>102.34375</v>
       </c>
       <c r="Q8" s="10">
-        <v>95.703125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>95.7</v>
+      </c>
+      <c r="R8" s="10">
+        <v>85.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D9" s="10">
         <v>131.39349295132962</v>
@@ -935,18 +952,21 @@
         <v>187.29463307776561</v>
       </c>
       <c r="Q9" s="10">
-        <v>113.91018619934282</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>113.9</v>
+      </c>
+      <c r="R9" s="10">
+        <v>139.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D10" s="10">
         <v>98.181818181818187</v>
@@ -988,18 +1008,21 @@
         <v>107.20081135902637</v>
       </c>
       <c r="Q10" s="10">
-        <v>108.21501014198785</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>108.4</v>
+      </c>
+      <c r="R10" s="10">
+        <v>103.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D11" s="10">
         <v>131.30000000000001</v>
@@ -1041,18 +1064,21 @@
         <v>155.38057742782152</v>
       </c>
       <c r="Q11" s="10">
-        <v>165.26684164479443</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>165.3</v>
+      </c>
+      <c r="R11" s="10">
+        <v>186.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D12" s="10">
         <v>24.193548387096776</v>
@@ -1094,18 +1120,21 @@
         <v>36.054971705739689</v>
       </c>
       <c r="Q12" s="10">
-        <v>48.504446240905416</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55.8</v>
+      </c>
+      <c r="R12" s="10">
+        <v>61.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D13" s="10">
         <v>146.66625946738333</v>
@@ -1147,18 +1176,21 @@
         <v>106.76765208893232</v>
       </c>
       <c r="Q13" s="10">
-        <v>97.361348644026393</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>101.8</v>
+      </c>
+      <c r="R13" s="10">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D14" s="11">
         <v>16.483516483516482</v>
@@ -1200,7 +1232,10 @@
         <v>32.967032967032964</v>
       </c>
       <c r="Q14" s="12">
-        <v>52.747252747252752</v>
+        <v>52.7</v>
+      </c>
+      <c r="R14" s="12">
+        <v>40.299999999999997</v>
       </c>
     </row>
   </sheetData>
